--- a/output/pdf_financials_xlsx/QMC.xlsx
+++ b/output/pdf_financials_xlsx/QMC.xlsx
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004552</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001075</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.503136</v>
+        <v>-0.507688</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.49877</v>
+        <v>-0.499845</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.503136</v>
+        <v>-0.507688</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.49877</v>
+        <v>-0.499845</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2823,40 +2823,40 @@
         <v>0.08089499999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000305</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001981</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000449</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.317095</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.196528</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.039531</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.010416</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.481612</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.256117</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.261592</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.131769</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.12149</v>
       </c>
     </row>
     <row r="35">
@@ -2927,40 +2927,40 @@
         <v>0.08089499999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000305</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001981</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000449</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.317095</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.000125</v>
+        <v>1.196653</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>5e-05</v>
+        <v>0.039581</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.000175</v>
+        <v>0.010591</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-0.000125</v>
+        <v>0.481487</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>5e-05</v>
+        <v>0.256167</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-5e-05</v>
+        <v>0.261542</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.131769</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.00055</v>
+        <v>0.12204</v>
       </c>
     </row>
     <row r="37">
@@ -3560,31 +3560,31 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.523651</v>
+        <v>0.206556</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.381586</v>
+        <v>0.185058</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.166553</v>
+        <v>0.127022</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.28351</v>
+        <v>0.273094</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.568636</v>
+        <v>0.087024</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.389127</v>
+        <v>0.13301</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.371421</v>
+        <v>0.109829</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.228244</v>
+        <v>0.09647500000000001</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.218512</v>
+        <v>0.097022</v>
       </c>
     </row>
     <row r="49">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -17223,7 +17223,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -19646,7 +19650,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -19996,7 +20000,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -31813,7 +31821,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">

--- a/output/pdf_financials_xlsx/QMC.xlsx
+++ b/output/pdf_financials_xlsx/QMC.xlsx
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.014872</v>
+        <v>0.036013</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.057508</v>
+        <v>0.083874</v>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.018633</v>
+        <v>0.081633</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.042292</v>
+        <v>0.177387</v>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.033505</v>
+        <v>0.117646</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.0998</v>
+        <v>0.261261</v>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.033505</v>
+        <v>-0.117646</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.0998</v>
+        <v>-0.261261</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
@@ -2887,28 +2887,28 @@
         <v>0</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.000125</v>
+        <v>0.00025</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5e-05</v>
+        <v>0.0003</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0.000175</v>
+        <v>0.000475</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>-0.000125</v>
+        <v>0.00035</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>5e-05</v>
+        <v>0.00025</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>-5e-05</v>
+        <v>0.0002</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0.00055</v>
+        <v>0.00075</v>
       </c>
     </row>
     <row r="36">
@@ -2939,28 +2939,28 @@
         <v>0.317095</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1.196653</v>
+        <v>1.196778</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.039581</v>
+        <v>0.039831</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.010591</v>
+        <v>0.010891</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.481487</v>
+        <v>0.481962</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.256167</v>
+        <v>0.256367</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.261542</v>
+        <v>0.261792</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.131769</v>
+        <v>0.131969</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.12204</v>
+        <v>0.12224</v>
       </c>
     </row>
     <row r="37">
@@ -3126,49 +3126,49 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.006382</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.089979</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.056231</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.180983</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.099814</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.001887</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.013566</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.057555</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.005783</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.001826</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.005277</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.064142</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.015411</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.002172</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.002719</v>
       </c>
     </row>
     <row r="41">
@@ -3178,49 +3178,49 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>0.006382</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>0.089979</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0</v>
+        <v>0.056231</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>0.180983</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.099814</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>0.001887</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>0.013566</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>0.057555</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>0.005783</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>0.001826</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0</v>
+        <v>0.005277</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0</v>
+        <v>0.064142</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0</v>
+        <v>0.015411</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0</v>
+        <v>0.002172</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0</v>
+        <v>0.002719</v>
       </c>
     </row>
     <row r="42">
@@ -3542,13 +3542,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.026382</v>
+        <v>0.02</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.103479</v>
+        <v>0.0135</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.098731</v>
+        <v>0.0425</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -3560,31 +3560,31 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.206556</v>
+        <v>0.19299</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.185058</v>
+        <v>0.127378</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.127022</v>
+        <v>0.120989</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.273094</v>
+        <v>0.270968</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.087024</v>
+        <v>0.081272</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.13301</v>
+        <v>0.06866800000000001</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.109829</v>
+        <v>0.094168</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.09647500000000001</v>
+        <v>0.09410300000000001</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.097022</v>
+        <v>0.09410300000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3829,28 +3829,28 @@
         <v>0</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0</v>
+        <v>0.105226</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0</v>
+        <v>0.106235</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0</v>
+        <v>0.09490899999999999</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0</v>
+        <v>0.08333599999999999</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>0</v>
+        <v>0.071065</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>0</v>
+        <v>0.06171</v>
       </c>
       <c r="O53" s="3" t="n">
-        <v>0</v>
+        <v>0.043322</v>
       </c>
       <c r="P53" s="3" t="n">
-        <v>0</v>
+        <v>0.024935</v>
       </c>
     </row>
     <row r="54">
@@ -4535,10 +4535,10 @@
         <v>0</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0</v>
+        <v>0.077089</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0</v>
+        <v>0.042089</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>0</v>
@@ -5766,49 +5766,49 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>0.765613</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>2.874374</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>2.996964</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>3.026964</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>3.026964</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>3.026964</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>4.278824</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>8.298781999999999</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>9.512596</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0</v>
+        <v>9.512596</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0</v>
+        <v>12.954196</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>0</v>
+        <v>13.235906</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>0</v>
+        <v>13.593906</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>0</v>
+        <v>13.923906</v>
       </c>
       <c r="P88" s="3" t="n">
-        <v>0</v>
+        <v>14.386506</v>
       </c>
     </row>
     <row r="89">
@@ -8698,7 +8698,11 @@
           <t>Other receivables – Note 3</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -8773,7 +8777,11 @@
           <t>Marketable securities – Note 4</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -9008,7 +9016,11 @@
           <t>Equipment – Note 5</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -9569,7 +9581,11 @@
           <t>Share capital – Note 7</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>0.765613</v>
       </c>
@@ -19737,7 +19753,11 @@
           <t>Other Receivables – Note 3</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -20433,7 +20453,11 @@
           <t>Share capital – Note 6</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -22424,7 +22448,11 @@
           <t>Due to related parties - Note 7</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -22693,7 +22721,11 @@
           <t>Write-off of mineral properties – Note 5</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>MineralProperties</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -24040,7 +24072,11 @@
           <t>Other Receivables – Note 4</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
       <c r="E183" s="5" t="n">
         <v>0.006382</v>
       </c>
@@ -30994,7 +31030,11 @@
           <t>Consulting - Note 8</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -31459,7 +31499,11 @@
           <t>Rent – Note 8</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/QMC.xlsx
+++ b/output/pdf_financials_xlsx/QMC.xlsx
@@ -27956,7 +27956,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
